--- a/data/Wohlen (AG)/investment_decision/Anglikon_SFH_2005-2014_investment_decision.xlsx
+++ b/data/Wohlen (AG)/investment_decision/Anglikon_SFH_2005-2014_investment_decision.xlsx
@@ -461,32 +461,32 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>scen_all_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>scen_all_candidate_unit</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_cu_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_cu_candidate_unit</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>scen_cp_dr_invested_available_unit</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_dr_candidate_unit</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>scen_all_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>scen_all_candidate_unit</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_candidate_unit</t>
         </is>
       </c>
     </row>
@@ -569,7 +569,7 @@
         <v>49675</v>
       </c>
       <c r="B4" t="n">
-        <v>77.0111190387444</v>
+        <v>81.047114268648</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -583,19 +583,19 @@
         <v>17782.50908211089</v>
       </c>
       <c r="F4" t="n">
-        <v>77.0111190387444</v>
+        <v>81.03811391465952</v>
       </c>
       <c r="G4" t="n">
         <v>17782.50908211089</v>
       </c>
       <c r="H4" t="n">
-        <v>77.01111903874437</v>
+        <v>81.04555462591688</v>
       </c>
       <c r="I4" t="n">
         <v>17782.50908211089</v>
       </c>
       <c r="J4" t="n">
-        <v>77.01111903874437</v>
+        <v>81.03811391465953</v>
       </c>
       <c r="K4" t="n">
         <v>17782.50908211089</v>
@@ -606,7 +606,7 @@
         <v>51502</v>
       </c>
       <c r="B5" t="n">
-        <v>77.9164591607769</v>
+        <v>81.047114268648</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -620,19 +620,19 @@
         <v>17782.50908211089</v>
       </c>
       <c r="F5" t="n">
-        <v>77.91645916077691</v>
+        <v>81.0381139146595</v>
       </c>
       <c r="G5" t="n">
         <v>17782.50908211089</v>
       </c>
       <c r="H5" t="n">
-        <v>77.91645916077692</v>
+        <v>81.04555462591681</v>
       </c>
       <c r="I5" t="n">
         <v>17782.50908211089</v>
       </c>
       <c r="J5" t="n">
-        <v>77.91645916077692</v>
+        <v>81.03811391465953</v>
       </c>
       <c r="K5" t="n">
         <v>17782.50908211089</v>
@@ -643,7 +643,7 @@
         <v>53328</v>
       </c>
       <c r="B6" t="n">
-        <v>77.91645916077691</v>
+        <v>81.047114268648</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -657,19 +657,19 @@
         <v>17782.50908211089</v>
       </c>
       <c r="F6" t="n">
-        <v>77.91645916077691</v>
+        <v>81.03811391465952</v>
       </c>
       <c r="G6" t="n">
         <v>17782.50908211089</v>
       </c>
       <c r="H6" t="n">
-        <v>77.91645916077692</v>
+        <v>81.04555462591681</v>
       </c>
       <c r="I6" t="n">
         <v>17782.50908211089</v>
       </c>
       <c r="J6" t="n">
-        <v>77.91645916077692</v>
+        <v>81.03811391465953</v>
       </c>
       <c r="K6" t="n">
         <v>17782.50908211089</v>
@@ -684,32 +684,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Anglikon_b_SFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Anglikon_b_SFH_2005-2014</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E7" t="n">
-        <v>26.67376362316633</v>
+        <v>39.42831640449438</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>26.67376362316633</v>
+        <v>18.98583346853757</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>12.84416075323076</v>
+        <v>18.98583346853757</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>12.84416075323076</v>
+        <v>39.42831640449438</v>
       </c>
     </row>
     <row r="8">
@@ -721,32 +721,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Anglikon_b_SFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Anglikon_b_SFH_2005-2014</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E8" t="n">
-        <v>26.67376362316633</v>
+        <v>39.42831640449438</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>26.67376362316633</v>
+        <v>27.04132631057192</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>18.2938053622519</v>
+        <v>27.04132631057192</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>18.2938053622519</v>
+        <v>39.42831640449438</v>
       </c>
     </row>
     <row r="9">
@@ -758,32 +758,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Anglikon_b_SFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Anglikon_b_SFH_2005-2014</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E9" t="n">
-        <v>26.67376362316633</v>
+        <v>39.42831640449438</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>26.67376362316633</v>
+        <v>31.09560015086719</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>21.03657380740153</v>
+        <v>31.09560015086719</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>21.03657380740153</v>
+        <v>39.42831640449438</v>
       </c>
     </row>
     <row r="10">
@@ -795,32 +795,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Anglikon_b_SFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Anglikon_b_SFH_2005-2014</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E10" t="n">
-        <v>26.67376362316633</v>
+        <v>39.42831640449438</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>26.67376362316633</v>
+        <v>33.39109391574365</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>22.58950489009386</v>
+        <v>33.39109391574365</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>22.58950489009386</v>
+        <v>39.42831640449438</v>
       </c>
     </row>
     <row r="11">
@@ -832,32 +832,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Anglikon_b_SFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Anglikon_b_SFH_2005-2014</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E11" t="n">
-        <v>26.67376362316633</v>
+        <v>39.42831640449438</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>26.67376362316633</v>
+        <v>34.80787290353657</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>23.5479741140638</v>
+        <v>34.80787290353657</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>23.5479741140638</v>
+        <v>39.42831640449438</v>
       </c>
     </row>
     <row r="12">
@@ -865,7 +865,7 @@
         <v>46023</v>
       </c>
       <c r="B12" t="n">
-        <v>0.005307912847058824</v>
+        <v>0.002919352065882353</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -879,19 +879,19 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.005307912847058824</v>
+        <v>0.002919352065882353</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.005307912847058824</v>
+        <v>0.002919352065882353</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.005307912847058824</v>
+        <v>0.002919352065882353</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -902,7 +902,7 @@
         <v>47849</v>
       </c>
       <c r="B13" t="n">
-        <v>0.005838704131764706</v>
+        <v>0.002919352065882353</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -916,19 +916,19 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.005838704131764706</v>
+        <v>0.002919352065882353</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.005838704131764706</v>
+        <v>0.002919352065882353</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.005838704131764706</v>
+        <v>0.002919352065882353</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -939,7 +939,7 @@
         <v>49675</v>
       </c>
       <c r="B14" t="n">
-        <v>0.006634891058823529</v>
+        <v>0.005145534519837507</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -953,19 +953,19 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.006634891058823529</v>
+        <v>0.005307912847058824</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.006634891058823529</v>
+        <v>0.005173672543971177</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.006634891058823529</v>
+        <v>0.005307912847058824</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -976,7 +976,7 @@
         <v>51502</v>
       </c>
       <c r="B15" t="n">
-        <v>0.007165682343529411</v>
+        <v>0.005145534519837507</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -990,19 +990,19 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.007165682343529411</v>
+        <v>0.005307912847058824</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.007165682343529411</v>
+        <v>0.005173672543971176</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.007165682343529411</v>
+        <v>0.005307912847058824</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1013,7 +1013,7 @@
         <v>53328</v>
       </c>
       <c r="B16" t="n">
-        <v>0.007165682343529411</v>
+        <v>0.005145534519837507</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1027,19 +1027,19 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.007165682343529411</v>
+        <v>0.005307912847058824</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.007165682343529411</v>
+        <v>0.005173672543971176</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.007165682343529411</v>
+        <v>0.005307912847058824</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1124,7 +1124,7 @@
         <v>49675</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>0.4020189499104935</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1138,19 +1138,19 @@
         <v>4.737312215999999</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>0.3534233887196265</v>
       </c>
       <c r="G19" t="n">
         <v>4.737312215999999</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>0.3532980310153119</v>
       </c>
       <c r="I19" t="n">
         <v>4.737312215999999</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>0.3903512739324639</v>
       </c>
       <c r="K19" t="n">
         <v>4.737312215999999</v>
@@ -1161,7 +1161,7 @@
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.4020189499104935</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1175,19 +1175,19 @@
         <v>4.737312215999999</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>0.3534233887196265</v>
       </c>
       <c r="G20" t="n">
         <v>4.737312215999999</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>0.3532980310153119</v>
       </c>
       <c r="I20" t="n">
         <v>4.737312215999999</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>0.3903512739324639</v>
       </c>
       <c r="K20" t="n">
         <v>4.737312215999999</v>
@@ -1198,7 +1198,7 @@
         <v>53328</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>0.4687352612039033</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1212,19 +1212,19 @@
         <v>4.737312215999999</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>0.4107090607426962</v>
       </c>
       <c r="G21" t="n">
         <v>4.737312215999999</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>0.3949337683769145</v>
       </c>
       <c r="I21" t="n">
         <v>4.737312215999999</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>0.468722113442537</v>
       </c>
       <c r="K21" t="n">
         <v>4.737312215999999</v>
@@ -1494,7 +1494,7 @@
         <v>49675</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>0.6711845814258312</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1508,19 +1508,19 @@
         <v>4.737312215999999</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>0.7049571750000001</v>
       </c>
       <c r="G29" t="n">
         <v>4.737312215999999</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>0.7049571750000001</v>
       </c>
       <c r="I29" t="n">
         <v>4.737312215999999</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>0.6760873453202889</v>
       </c>
       <c r="K29" t="n">
         <v>4.737312215999999</v>
@@ -1531,7 +1531,7 @@
         <v>51502</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>0.6966870835129706</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1545,19 +1545,19 @@
         <v>4.737312215999999</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>0.731323392379108</v>
       </c>
       <c r="G30" t="n">
         <v>4.737312215999999</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>0.7313155290483848</v>
       </c>
       <c r="I30" t="n">
         <v>4.737312215999999</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.7049571750000001</v>
       </c>
       <c r="K30" t="n">
         <v>4.737312215999999</v>
@@ -1568,7 +1568,7 @@
         <v>53328</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>0.7721308013957494</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1582,19 +1582,19 @@
         <v>4.737312215999999</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>0.8281101492783667</v>
       </c>
       <c r="G31" t="n">
         <v>4.737312215999999</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>0.84594861</v>
       </c>
       <c r="I31" t="n">
         <v>4.737312215999999</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>0.7722381039068007</v>
       </c>
       <c r="K31" t="n">
         <v>4.737312215999999</v>
@@ -1992,7 +1992,7 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>179.7367755496497</v>
+        <v>91.32888203015514</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -2004,7 +2004,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>91.32888203015514</v>
+        <v>179.7367755496497</v>
       </c>
     </row>
     <row r="43">
@@ -2029,7 +2029,7 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>179.7367755496497</v>
+        <v>128.1911746930678</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -2041,7 +2041,7 @@
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>128.1911746930678</v>
+        <v>179.7367755496497</v>
       </c>
     </row>
     <row r="44">
@@ -2066,7 +2066,7 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>179.7367755496497</v>
+        <v>146.0529813100824</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -2078,7 +2078,7 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>146.0529813100824</v>
+        <v>179.7367755496497</v>
       </c>
     </row>
     <row r="45">
@@ -2103,7 +2103,7 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>179.7367755496497</v>
+        <v>155.8739024353837</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -2115,7 +2115,7 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>155.8739024353837</v>
+        <v>179.7367755496497</v>
       </c>
     </row>
     <row r="46">
@@ -2140,7 +2140,7 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>179.7367755496497</v>
+        <v>161.7960910887763</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -2152,7 +2152,7 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>161.7960910887763</v>
+        <v>179.7367755496497</v>
       </c>
     </row>
     <row r="47">
@@ -2362,7 +2362,7 @@
         <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>29.06617175354291</v>
+        <v>6.395209113145975</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -2374,7 +2374,7 @@
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>6.395209113145975</v>
+        <v>29.06617175354291</v>
       </c>
     </row>
     <row r="53">
@@ -2399,7 +2399,7 @@
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>29.06617175354291</v>
+        <v>10.41478914243237</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -2411,7 +2411,7 @@
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>10.41478914243237</v>
+        <v>29.06617175354291</v>
       </c>
     </row>
     <row r="54">
@@ -2419,7 +2419,7 @@
         <v>49675</v>
       </c>
       <c r="B54" t="n">
-        <v>4.714534453848128</v>
+        <v>4.843599306269652</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2433,22 +2433,22 @@
         <v>29.06617175354291</v>
       </c>
       <c r="F54" t="n">
-        <v>4.344378237200568</v>
+        <v>4.739270870761521</v>
       </c>
       <c r="G54" t="n">
-        <v>29.06617175354291</v>
+        <v>13.10690205329574</v>
       </c>
       <c r="H54" t="n">
-        <v>4.344378237200567</v>
+        <v>4.842673242147913</v>
       </c>
       <c r="I54" t="n">
         <v>13.10690205329574</v>
       </c>
       <c r="J54" t="n">
-        <v>4.714534453848127</v>
+        <v>4.739270870761523</v>
       </c>
       <c r="K54" t="n">
-        <v>13.10690205329574</v>
+        <v>29.06617175354291</v>
       </c>
     </row>
     <row r="55">
@@ -2456,7 +2456,7 @@
         <v>51502</v>
       </c>
       <c r="B55" t="n">
-        <v>5.29551677352937</v>
+        <v>5.739304225014537</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2470,22 +2470,22 @@
         <v>29.06617175354291</v>
       </c>
       <c r="F55" t="n">
-        <v>4.941049084592805</v>
+        <v>5.350238928432236</v>
       </c>
       <c r="G55" t="n">
-        <v>29.06617175354291</v>
+        <v>15.00498643641032</v>
       </c>
       <c r="H55" t="n">
-        <v>4.941049084592806</v>
+        <v>5.739298445162063</v>
       </c>
       <c r="I55" t="n">
         <v>15.00498643641032</v>
       </c>
       <c r="J55" t="n">
-        <v>5.29551677352937</v>
+        <v>5.350238928432233</v>
       </c>
       <c r="K55" t="n">
-        <v>15.00498643641032</v>
+        <v>29.06617175354291</v>
       </c>
     </row>
     <row r="56">
@@ -2493,7 +2493,7 @@
         <v>53328</v>
       </c>
       <c r="B56" t="n">
-        <v>5.29551677352937</v>
+        <v>5.739304225014537</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2507,22 +2507,22 @@
         <v>29.06617175354291</v>
       </c>
       <c r="F56" t="n">
-        <v>4.941049084592805</v>
+        <v>5.350238928432236</v>
       </c>
       <c r="G56" t="n">
-        <v>29.06617175354291</v>
+        <v>16.39913823795342</v>
       </c>
       <c r="H56" t="n">
-        <v>4.941049084592806</v>
+        <v>5.739298445162063</v>
       </c>
       <c r="I56" t="n">
         <v>16.39913823795342</v>
       </c>
       <c r="J56" t="n">
-        <v>5.29551677352937</v>
+        <v>5.350238928432234</v>
       </c>
       <c r="K56" t="n">
-        <v>16.39913823795342</v>
+        <v>29.06617175354291</v>
       </c>
     </row>
     <row r="57">
@@ -2547,7 +2547,7 @@
         <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>29.06617175354291</v>
+        <v>6.395209113145975</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -2559,7 +2559,7 @@
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>6.395209113145975</v>
+        <v>29.06617175354291</v>
       </c>
     </row>
     <row r="58">
@@ -2584,7 +2584,7 @@
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>29.06617175354291</v>
+        <v>10.41478914243237</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -2596,7 +2596,7 @@
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>10.41478914243237</v>
+        <v>29.06617175354291</v>
       </c>
     </row>
     <row r="59">
@@ -2621,7 +2621,7 @@
         <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>29.06617175354291</v>
+        <v>13.10690205329574</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -2633,7 +2633,7 @@
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>13.10690205329574</v>
+        <v>29.06617175354291</v>
       </c>
     </row>
     <row r="60">
@@ -2658,7 +2658,7 @@
         <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>29.06617175354291</v>
+        <v>15.00498643641032</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -2670,7 +2670,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>15.00498643641032</v>
+        <v>29.06617175354291</v>
       </c>
     </row>
     <row r="61">
@@ -2695,7 +2695,7 @@
         <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>29.06617175354291</v>
+        <v>16.39913823795342</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -2707,7 +2707,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>16.39913823795342</v>
+        <v>29.06617175354291</v>
       </c>
     </row>
     <row r="62">
@@ -2789,7 +2789,7 @@
         <v>49675</v>
       </c>
       <c r="B64" t="n">
-        <v>3.875433960614699</v>
+        <v>0.5279907471612069</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2803,19 +2803,19 @@
         <v>29.06617175354291</v>
       </c>
       <c r="F64" t="n">
-        <v>4.245590177262258</v>
+        <v>0.6241639408214944</v>
       </c>
       <c r="G64" t="n">
         <v>29.06617175354291</v>
       </c>
       <c r="H64" t="n">
-        <v>4.245590177262263</v>
+        <v>0.5275036153481369</v>
       </c>
       <c r="I64" t="n">
         <v>29.06617175354291</v>
       </c>
       <c r="J64" t="n">
-        <v>3.875433960614702</v>
+        <v>0.6241639408214918</v>
       </c>
       <c r="K64" t="n">
         <v>29.06617175354291</v>
@@ -2826,7 +2826,7 @@
         <v>51502</v>
       </c>
       <c r="B65" t="n">
-        <v>5.274480902947446</v>
+        <v>1.632285828416323</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2840,19 +2840,19 @@
         <v>29.06617175354291</v>
       </c>
       <c r="F65" t="n">
-        <v>5.628948591884011</v>
+        <v>2.01319588315078</v>
       </c>
       <c r="G65" t="n">
         <v>29.06617175354291</v>
       </c>
       <c r="H65" t="n">
-        <v>5.628948591884009</v>
+        <v>1.630878412333988</v>
       </c>
       <c r="I65" t="n">
         <v>29.06617175354291</v>
       </c>
       <c r="J65" t="n">
-        <v>5.274480902947446</v>
+        <v>2.013195883150783</v>
       </c>
       <c r="K65" t="n">
         <v>29.06617175354291</v>
@@ -2863,7 +2863,7 @@
         <v>53328</v>
       </c>
       <c r="B66" t="n">
-        <v>5.274480902947446</v>
+        <v>1.632285828416323</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2877,19 +2877,19 @@
         <v>29.06617175354291</v>
       </c>
       <c r="F66" t="n">
-        <v>5.628948591884011</v>
+        <v>2.01319588315078</v>
       </c>
       <c r="G66" t="n">
         <v>29.06617175354291</v>
       </c>
       <c r="H66" t="n">
-        <v>5.628948591884009</v>
+        <v>1.630878412333988</v>
       </c>
       <c r="I66" t="n">
         <v>29.06617175354291</v>
       </c>
       <c r="J66" t="n">
-        <v>5.274480902947446</v>
+        <v>2.013195883150783</v>
       </c>
       <c r="K66" t="n">
         <v>29.06617175354291</v>
@@ -3108,13 +3108,13 @@
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>1.77952727525052</v>
+        <v>29.06617175354291</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>1.77952727525052</v>
+        <v>29.06617175354291</v>
       </c>
     </row>
     <row r="73">
@@ -3145,13 +3145,13 @@
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>3.174371762696704</v>
+        <v>29.06617175354291</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>3.174371762696704</v>
+        <v>29.06617175354291</v>
       </c>
     </row>
     <row r="74">
@@ -3182,13 +3182,13 @@
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>4.310847478741441</v>
+        <v>29.06617175354291</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>4.310847478741441</v>
+        <v>29.06617175354291</v>
       </c>
     </row>
     <row r="75">
@@ -3219,13 +3219,13 @@
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>5.26337117267812</v>
+        <v>29.06617175354291</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>5.26337117267812</v>
+        <v>29.06617175354291</v>
       </c>
     </row>
     <row r="76">
@@ -3256,13 +3256,13 @@
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>6.077328426851443</v>
+        <v>29.06617175354291</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>6.077328426851443</v>
+        <v>29.06617175354291</v>
       </c>
     </row>
     <row r="77">
@@ -3293,13 +3293,13 @@
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>1.77952727525052</v>
+        <v>29.06617175354291</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>1.77952727525052</v>
+        <v>29.06617175354291</v>
       </c>
     </row>
     <row r="78">
@@ -3330,13 +3330,13 @@
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>3.174371762696704</v>
+        <v>29.06617175354291</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>3.174371762696704</v>
+        <v>29.06617175354291</v>
       </c>
     </row>
     <row r="79">
@@ -3367,13 +3367,13 @@
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>4.310847478741441</v>
+        <v>29.06617175354291</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>4.310847478741441</v>
+        <v>29.06617175354291</v>
       </c>
     </row>
     <row r="80">
@@ -3404,13 +3404,13 @@
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>5.26337117267812</v>
+        <v>29.06617175354291</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>5.26337117267812</v>
+        <v>29.06617175354291</v>
       </c>
     </row>
     <row r="81">
@@ -3441,13 +3441,13 @@
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>6.077328426851443</v>
+        <v>29.06617175354291</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>6.077328426851443</v>
+        <v>29.06617175354291</v>
       </c>
     </row>
     <row r="82">
@@ -3470,7 +3470,7 @@
         <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>1</v>
+        <v>0.2712070570783821</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
@@ -3482,7 +3482,7 @@
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>0.2712070570783821</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -3505,7 +3505,7 @@
         <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>1</v>
+        <v>0.4370978189737727</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -3517,7 +3517,7 @@
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>0.4370978189737727</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
@@ -3540,7 +3540,7 @@
         <v>0</v>
       </c>
       <c r="G84" t="n">
-        <v>1</v>
+        <v>0.5456964388783678</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -3552,7 +3552,7 @@
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>0.5456964388783678</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
@@ -3575,7 +3575,7 @@
         <v>0</v>
       </c>
       <c r="G85" t="n">
-        <v>1</v>
+        <v>0.6207578627767205</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
@@ -3587,7 +3587,7 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>0.6207578627767205</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
@@ -3610,7 +3610,7 @@
         <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>1</v>
+        <v>0.6749874416447547</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -3622,7 +3622,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>0.6749874416447547</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
@@ -3645,7 +3645,7 @@
         <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>1</v>
+        <v>0.2712070570783821</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -3657,7 +3657,7 @@
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>0.2712070570783821</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
@@ -3680,7 +3680,7 @@
         <v>0</v>
       </c>
       <c r="G88" t="n">
-        <v>1</v>
+        <v>0.4370978189737727</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -3692,7 +3692,7 @@
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>0.4370978189737727</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="G89" t="n">
-        <v>1</v>
+        <v>0.5456964388783678</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -3727,7 +3727,7 @@
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>0.5456964388783678</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -3750,7 +3750,7 @@
         <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>1</v>
+        <v>0.6207578627767205</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -3762,7 +3762,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>0.6207578627767205</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
@@ -3785,7 +3785,7 @@
         <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>1</v>
+        <v>0.6749874416447547</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -3797,7 +3797,7 @@
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>0.6749874416447547</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -3820,7 +3820,7 @@
         <v>0</v>
       </c>
       <c r="G92" t="n">
-        <v>1</v>
+        <v>0.2712070570783821</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
@@ -3832,7 +3832,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>0.2712070570783821</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
@@ -3855,7 +3855,7 @@
         <v>0</v>
       </c>
       <c r="G93" t="n">
-        <v>1</v>
+        <v>0.4370978189737727</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
@@ -3867,7 +3867,7 @@
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>0.4370978189737727</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
@@ -3890,7 +3890,7 @@
         <v>0</v>
       </c>
       <c r="G94" t="n">
-        <v>1</v>
+        <v>0.5456964388783678</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
@@ -3902,7 +3902,7 @@
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>0.5456964388783678</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
@@ -3925,7 +3925,7 @@
         <v>0</v>
       </c>
       <c r="G95" t="n">
-        <v>1</v>
+        <v>0.6207578627767205</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -3937,7 +3937,7 @@
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>0.6207578627767205</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
@@ -3960,7 +3960,7 @@
         <v>0</v>
       </c>
       <c r="G96" t="n">
-        <v>1</v>
+        <v>0.6749874416447547</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -3972,7 +3972,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>0.6749874416447547</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
